--- a/lcr_analyses/clustering/carriers/AlcoR/cluster_summaries_pam.xlsx
+++ b/lcr_analyses/clustering/carriers/AlcoR/cluster_summaries_pam.xlsx
@@ -12,6 +12,10 @@
     <sheet name="k4" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="k5" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="k6" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="k7" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="k8" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="k9" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="k10" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4520,4 +4524,5858 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AU8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>cluster</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>size</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>median_n_lcr</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>median_coverage</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>median_mean_lcr_length</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>prop_domain_intrinsic</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>prop_domain_edge</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>prop_domain_adjacent</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>prop_interdomain_linker</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>prop_distal_terminal</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>prop_sig_rg_rgg_repeat_region</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>prop_sig_sr_rs_repeat_region</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>prop_sig_gs_rich_neutral_region</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>prop_sig_basic_enriched_region</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>prop_sig_arginine_rich_rna_contact_region</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>prop_sig_acidic_region</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>prop_sig_mixed_charge_polyampholyte</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>prop_sig_polar_linker</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>prop_sig_hydrophobic_region</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>prop_sig_aromatic_sticker_region</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>prop_sig_aromatic_aggregation_prone_region</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>prop_sig_cation_pi_rich_neighborhood</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>prop_sig_disorder_rich_spacer_region</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>prop_sig_serine_rich_region</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>prop_sig_glutamine_rich_region</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>prop_sig_glycine_rich_region</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>prop_sig_proline_rich_disordered_region</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>prop_sig_unmapped_physicochemical_properties</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>median_frac_polar</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>median_frac_hydrophobic</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>median_frac_strong_hydro</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>median_frac_aromatic</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>median_frac_disorder</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>median_frac_positive</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>median_frac_negative</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>median_fcr</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>median_ncpr</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>median_frac_GS</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>class_mRNA</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>class_unknown</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>class_tRNA</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>class_ribosomal protein</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>class_snRNA</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>class_pre-rRNA</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>class_ncRNA</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>class_diverse</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>class_snoRNA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" t="n">
+        <v>147</v>
+      </c>
+      <c r="C2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.23125</v>
+      </c>
+      <c r="E2" t="n">
+        <v>45.33333333333334</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.3061224489795918</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.1360544217687075</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.1292517006802721</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.108843537414966</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.01360544217687075</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.01360544217687075</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.07482993197278912</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.05442176870748299</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.08163265306122448</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.1156462585034014</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.08843537414965986</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.891156462585034</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.09523809523809523</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.08843537414965986</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.006802721088435374</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.006802721088435374</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0.01360544217687075</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.1768707482993197</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0.5049999999999999</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.6311475409836066</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0.3214285714285715</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0.1166666666666667</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0.4964539007092199</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0.1219512195121951</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0.1055900621118013</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0.2325581395348837</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0.008385744234800839</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0.1333333333333333</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>53</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>36</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>18</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="n">
+        <v>246</v>
+      </c>
+      <c r="C3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.1053548220440914</v>
+      </c>
+      <c r="E3" t="n">
+        <v>26.41666666666666</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.1585365853658537</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.1747967479674797</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.04878048780487805</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.2967479674796748</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.01219512195121951</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.01219512195121951</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.03252032520325204</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.05691056910569105</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.08536585365853659</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.1097560975609756</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.03252032520325204</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.004065040650406504</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.1056910569105691</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.7764227642276422</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.08943089430894309</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.1219512195121951</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.008130081300813009</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0.004065040650406504</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.02439024390243903</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.2073170731707317</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.5142085055391161</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.6041137901861252</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.3117113327725033</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0.109906973685172</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0.1141461144718474</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0.1052631578947368</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0.2317894736842105</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0.1363822176801227</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>104</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>58</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>21</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>25</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="n">
+        <v>206</v>
+      </c>
+      <c r="C4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.9389940811400989</v>
+      </c>
+      <c r="E4" t="n">
+        <v>193</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.05339805825242718</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.8786407766990292</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.1116504854368932</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.04368932038834952</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.1407766990291262</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.1262135922330097</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.08737864077669903</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.07766990291262135</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.02427184466019417</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.02427184466019417</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.03883495145631068</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.1310679611650485</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.01456310679611651</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.7718446601941747</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.1019417475728155</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.03398058252427184</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.05825242718446602</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.5297025379931568</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.6001262682343386</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.2951516722841586</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.1055454284605128</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.5294117647058824</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.1325438161375661</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.117010647844066</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.2622735593784478</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0.00951032885930321</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.1396203830369357</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>88</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>53</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>11</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="n">
+        <v>75</v>
+      </c>
+      <c r="C5" t="n">
+        <v>7</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.2710706150341686</v>
+      </c>
+      <c r="E5" t="n">
+        <v>23.57142857142857</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.7466666666666667</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.8266666666666667</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.7866666666666666</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.2666666666666667</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.8533333333333334</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.01333333333333333</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.06666666666666667</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.05333333333333334</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.1466666666666667</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.4666666666666667</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.2666666666666667</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0.5192307692307693</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.5897435897435898</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0.3031674208144796</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0.0945945945945946</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0.5396825396825397</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0.1279069767441861</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0.2429577464788732</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>-9.942295742911849e-18</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0.1290322580645161</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>32</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>16</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>8</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="n">
+        <v>108</v>
+      </c>
+      <c r="C6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.07513384382398738</v>
+      </c>
+      <c r="E6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.02777777777777778</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.1481481481481481</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.03703703703703703</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.7037037037037037</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.06481481481481481</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.09259259259259259</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.06481481481481481</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.05555555555555555</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.1018518518518518</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.1851851851851852</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.4907407407407408</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.009259259259259259</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.01851851851851852</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.1574074074074074</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.03703703703703703</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.1851851851851852</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.02777777777777778</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.1481481481481481</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.6049258607690375</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.5138189036494121</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0.2307692307692308</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0.06742424242424241</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.6099033816425121</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0.1634910601408705</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0.3403222146584979</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0.1422787738577212</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>43</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>25</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>13</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="n">
+        <v>82</v>
+      </c>
+      <c r="C7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.6841732657151486</v>
+      </c>
+      <c r="E7" t="n">
+        <v>137.5</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.2073170731707317</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.9146341463414634</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.2804878048780488</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.1951219512195122</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.8780487804878049</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.06097560975609756</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.07317073170731707</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.08536585365853659</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.07317073170731707</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.1219512195121951</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.1951219512195122</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.6707317073170732</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.03658536585365853</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.9512195121951219</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.7195121951219512</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.1951219512195122</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0.02439024390243903</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.1951219512195122</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.5410398464641633</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.5805827980738566</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0.2768995158581168</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0.09596254749869712</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0.5387863607136345</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0.1328108363894475</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0.1334914580509678</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0.268940511307768</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0.003573728674437105</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0.1466531180489991</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>23</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>42</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="n">
+        <v>104</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.2748733348064903</v>
+      </c>
+      <c r="E8" t="n">
+        <v>63.75</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.6826923076923077</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.1153846153846154</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.0576923076923077</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.1634615384615385</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.07692307692307693</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.01923076923076923</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.09615384615384616</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.1442307692307692</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.1057692307692308</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.1057692307692308</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.0576923076923077</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.03846153846153846</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.7019230769230769</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0.1346153846153846</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.1634615384615385</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0.5467178903433884</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0.5749698916097953</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0.2692257189127675</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0.06507622811970637</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0.5517460317460318</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0.1496753246753246</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0.1239006449549598</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0.2858109250803315</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0.04340659340659341</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0.1408043032786885</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>34</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>24</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>8</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>9</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>8</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AU9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>cluster</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>size</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>median_n_lcr</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>median_coverage</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>median_mean_lcr_length</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>prop_domain_intrinsic</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>prop_domain_edge</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>prop_domain_adjacent</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>prop_interdomain_linker</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>prop_distal_terminal</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>prop_sig_rg_rgg_repeat_region</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>prop_sig_sr_rs_repeat_region</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>prop_sig_gs_rich_neutral_region</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>prop_sig_basic_enriched_region</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>prop_sig_arginine_rich_rna_contact_region</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>prop_sig_acidic_region</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>prop_sig_mixed_charge_polyampholyte</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>prop_sig_polar_linker</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>prop_sig_hydrophobic_region</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>prop_sig_aromatic_sticker_region</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>prop_sig_aromatic_aggregation_prone_region</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>prop_sig_cation_pi_rich_neighborhood</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>prop_sig_disorder_rich_spacer_region</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>prop_sig_serine_rich_region</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>prop_sig_glutamine_rich_region</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>prop_sig_glycine_rich_region</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>prop_sig_proline_rich_disordered_region</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>prop_sig_unmapped_physicochemical_properties</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>median_frac_polar</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>median_frac_hydrophobic</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>median_frac_strong_hydro</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>median_frac_aromatic</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>median_frac_disorder</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>median_frac_positive</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>median_frac_negative</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>median_fcr</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>median_ncpr</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>median_frac_GS</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>class_mRNA</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>class_unknown</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>class_tRNA</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>class_ribosomal protein</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>class_snRNA</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>class_pre-rRNA</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>class_ncRNA</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>class_diverse</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>class_snoRNA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" t="n">
+        <v>138</v>
+      </c>
+      <c r="C2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.219785039679937</v>
+      </c>
+      <c r="E2" t="n">
+        <v>44</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.3260869565217391</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.1231884057971015</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.1304347826086956</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.05072463768115942</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.007246376811594203</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.01449275362318841</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.06521739130434782</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.04347826086956522</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.06521739130434782</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.1231884057971015</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.09420289855072464</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.8913043478260869</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.1014492753623188</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.07971014492753623</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.007246376811594203</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0.01449275362318841</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.1811594202898551</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.6318190530956489</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0.3233907792016497</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0.117156862745098</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0.4927404718693285</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0.1221109809351369</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0.1042736333434008</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0.2323736536868268</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0.007835859366945046</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0.1319718017831226</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>50</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>31</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>18</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="n">
+        <v>173</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.1131386861313869</v>
+      </c>
+      <c r="E3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.2023121387283237</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.1849710982658959</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.04624277456647399</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.01734104046242774</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.0115606936416185</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.03468208092485549</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.06358381502890173</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.08670520231213873</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.09248554913294797</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.04624277456647399</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.1040462427745665</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.6878612716763006</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.09826589595375723</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.138728323699422</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.005780346820809248</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0.005780346820809248</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.02312138728323699</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.2427745664739884</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.612</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0.1046511627906977</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0.1181286549707602</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0.103448275862069</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0.2377850162866449</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0.1322115384615385</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>74</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>35</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>16</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>21</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="n">
+        <v>202</v>
+      </c>
+      <c r="C4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.9404049844236759</v>
+      </c>
+      <c r="E4" t="n">
+        <v>193.25</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.05445544554455446</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.8762376237623762</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.1089108910891089</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.04455445544554455</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.1237623762376238</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.1237623762376238</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.0891089108910891</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.07920792079207921</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.02475247524752475</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.02475247524752475</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.0396039603960396</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.1336633663366337</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.01485148514851485</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.7673267326732673</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.103960396039604</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.0297029702970297</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.0594059405940594</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.5289140543435129</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.6016312385969836</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.2970654153242751</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.1055454284605128</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.5291986359761296</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.1325438161375661</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.1176954537808058</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.2622735593784478</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0.008963716695675458</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.1387179393976675</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>52</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>11</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="n">
+        <v>67</v>
+      </c>
+      <c r="C5" t="n">
+        <v>7</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.2861842105263158</v>
+      </c>
+      <c r="E5" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.746268656716418</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.9253731343283582</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.8059701492537313</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.2985074626865671</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.835820895522388</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.01492537313432836</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.05970149253731343</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.05970149253731343</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.1492537313432836</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.2388059701492537</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.5223880597014925</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.3134328358208955</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.5074626865671642</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.9104477611940298</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.2686567164179104</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.7313432835820896</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0.1343283582089552</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.7164179104477612</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0.5176470588235295</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.5925925925925926</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0.3052631578947368</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0.0945945945945946</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0.5371900826446281</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0.1260504201680673</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0.1229508196721311</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0.2377049180327869</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>-0.004926108374384237</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0.1292246520874752</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>29</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>14</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>6</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="n">
+        <v>92</v>
+      </c>
+      <c r="C6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.06116233660573846</v>
+      </c>
+      <c r="E6" t="n">
+        <v>20.75</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.1304347826086956</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.03260869565217391</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.1521739130434783</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.04347826086956522</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.6521739130434783</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.05434782608695652</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.09782608695652174</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.06521739130434782</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.04347826086956522</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.09782608695652174</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.2065217391304348</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.5108695652173914</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.0108695652173913</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.0108695652173913</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.108695652173913</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.02173913043478261</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.2173913043478261</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.02173913043478261</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.1304347826086956</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.6133823059725327</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0.2077339809452644</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0.06355611601513242</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.6202167514048702</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0.1695210449927431</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0.1720841842523259</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0.3569340016708438</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0.1359437751004016</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>38</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>11</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79</v>
+      </c>
+      <c r="C7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.6905487804878049</v>
+      </c>
+      <c r="E7" t="n">
+        <v>137</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.2025316455696203</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.9493670886075949</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.2025316455696203</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.8734177215189873</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.06329113924050633</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.0759493670886076</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.08860759493670886</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.0759493670886076</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.1265822784810127</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.189873417721519</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.6835443037974683</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.0379746835443038</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.9493670886075949</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.7215189873417721</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.189873417721519</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0.02531645569620253</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.189873417721519</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.5405777166437414</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.5817174515235457</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0.2779369627507163</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0.0964722822174226</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0.5385656292286874</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0.1327102803738318</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0.1334569045412419</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0.2684365781710915</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0.004993757802746566</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0.1464530892448513</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>22</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>41</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="n">
+        <v>102</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.2748733348064903</v>
+      </c>
+      <c r="E8" t="n">
+        <v>63.75</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.1274509803921569</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.6862745098039216</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.1176470588235294</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.05882352941176471</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.1470588235294118</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.06862745098039216</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.0196078431372549</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.09803921568627451</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.1372549019607843</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.107843137254902</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.107843137254902</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.04901960784313725</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.0392156862745098</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.7058823529411765</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0.1372549019607843</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0.5482281284606867</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0.5749698916097953</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0.2692257189127675</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0.06371753246753246</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0.5505555555555556</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0.1493021903469665</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0.1247568093385214</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0.2893670174045397</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0.04197651663405088</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0.1401654411764706</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>33</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>24</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>8</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>8</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>8</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="n">
+        <v>115</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.1410459587955626</v>
+      </c>
+      <c r="E9" t="n">
+        <v>36</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.09565217391304348</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.1217391304347826</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.208695652173913</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.04347826086956522</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.02608695652173913</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.04347826086956522</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.02608695652173913</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.06956521739130435</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.1130434782608696</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.1739130434782609</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.06086956521739131</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.008695652173913044</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.09565217391304348</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.8869565217391304</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.1043478260869565</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.1304347826086956</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.01739130434782609</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0.02608695652173913</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.1565217391304348</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0.5341130604288499</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0.5796344647519582</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0.287037037037037</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0.1082802547770701</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0.521484375</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0.1171171171171171</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0.1091445427728614</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0.2437810945273632</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0.007117437722419928</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0.1473684210526316</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>46</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>36</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>8</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>8</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AU10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>cluster</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>size</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>median_n_lcr</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>median_coverage</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>median_mean_lcr_length</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>prop_domain_intrinsic</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>prop_domain_edge</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>prop_domain_adjacent</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>prop_interdomain_linker</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>prop_distal_terminal</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>prop_sig_rg_rgg_repeat_region</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>prop_sig_sr_rs_repeat_region</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>prop_sig_gs_rich_neutral_region</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>prop_sig_basic_enriched_region</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>prop_sig_arginine_rich_rna_contact_region</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>prop_sig_acidic_region</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>prop_sig_mixed_charge_polyampholyte</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>prop_sig_polar_linker</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>prop_sig_hydrophobic_region</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>prop_sig_aromatic_sticker_region</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>prop_sig_aromatic_aggregation_prone_region</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>prop_sig_cation_pi_rich_neighborhood</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>prop_sig_disorder_rich_spacer_region</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>prop_sig_serine_rich_region</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>prop_sig_glutamine_rich_region</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>prop_sig_glycine_rich_region</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>prop_sig_proline_rich_disordered_region</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>prop_sig_unmapped_physicochemical_properties</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>median_frac_polar</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>median_frac_hydrophobic</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>median_frac_strong_hydro</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>median_frac_aromatic</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>median_frac_disorder</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>median_frac_positive</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>median_frac_negative</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>median_fcr</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>median_ncpr</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>median_frac_GS</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>class_mRNA</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>class_unknown</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>class_tRNA</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>class_pre-rRNA</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>class_ncRNA</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>class_snRNA</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>class_ribosomal protein</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>class_snoRNA</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>class_diverse</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" t="n">
+        <v>75</v>
+      </c>
+      <c r="C2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.06425702811244979</v>
+      </c>
+      <c r="E2" t="n">
+        <v>22</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.1066666666666667</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.1733333333333333</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.7066666666666667</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.05333333333333334</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.1466666666666667</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.05333333333333334</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.09333333333333334</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.06666666666666667</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.1733333333333333</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.02666666666666667</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.01333333333333333</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.02666666666666667</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.1466666666666667</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.6933333333333334</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.01333333333333333</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.1466666666666667</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0.5507246376811594</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.5081967213114754</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0.1869918699186992</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0.04545454545454546</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0.6746987951807228</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0.1408450704225352</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0.1224489795918367</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0.2709163346613546</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0.03370786516853932</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0.1991869918699187</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>32</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>18</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="n">
+        <v>144</v>
+      </c>
+      <c r="C3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.2157474938126273</v>
+      </c>
+      <c r="E3" t="n">
+        <v>38.08333333333333</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.1944444444444444</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.1319444444444444</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.04166666666666666</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.01388888888888889</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.01388888888888889</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.04166666666666666</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.04861111111111111</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.06944444444444445</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.1180555555555556</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.8611111111111112</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.1319444444444444</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.006944444444444444</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.02777777777777778</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.2430555555555556</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.5060715337062114</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.6148887862695298</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.3244673443810054</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0.1104355716878403</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0.4849445756241622</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0.1121213675652107</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0.1101724137931034</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0.2300695432274379</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0.1291419793723941</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>58</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>32</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>14</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>19</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="n">
+        <v>188</v>
+      </c>
+      <c r="C4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.9403725168912085</v>
+      </c>
+      <c r="E4" t="n">
+        <v>200.75</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.05851063829787234</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.9468085106382979</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.1223404255319149</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.04787234042553191</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.1436170212765958</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.1329787234042553</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.09574468085106383</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.0797872340425532</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.02127659574468085</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.02659574468085106</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.03191489361702127</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.1117021276595745</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.01063829787234043</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.7819148936170213</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.101063829787234</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.02127659574468085</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.05851063829787234</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.5265705555233737</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.6016312385969836</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.2970654153242751</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.1039314021182577</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.5294117647058824</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.1321097883597884</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.1164255320498186</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.2590248476324426</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0.01060362540693533</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.140360661517911</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>81</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>49</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>11</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="n">
+        <v>64</v>
+      </c>
+      <c r="C5" t="n">
+        <v>7</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.287286861817465</v>
+      </c>
+      <c r="E5" t="n">
+        <v>24</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.78125</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.921875</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.796875</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.828125</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.015625</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.046875</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.15625</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.53125</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.328125</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.53125</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.953125</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.28125</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.71875</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.71875</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0.5137309943157954</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.5983193277310924</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0.305713089881762</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0.09547979797979797</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0.5367768595041322</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0.1212059274399591</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0.1226998996319839</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0.2376024590163934</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>-0.005210306934444858</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0.1291284550759956</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>28</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>14</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>6</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>6</v>
+      </c>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="n">
+        <v>83</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.07656826568265683</v>
+      </c>
+      <c r="E6" t="n">
+        <v>19</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.1566265060240964</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.1325301204819277</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.1686746987951807</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.108433734939759</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.1807228915662651</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.02409638554216868</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.01204819277108434</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.03614457831325301</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.08433734939759036</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.1807228915662651</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.2048192771084337</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.5783132530120482</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.01204819277108434</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.04819277108433735</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.03614457831325301</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.02409638554216868</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.07228915662650602</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.01204819277108434</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.1927710843373494</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.5553602811950791</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0.07246376811594203</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0.1686746987951807</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0.3529411764705883</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>39</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>12</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="n">
+        <v>83</v>
+      </c>
+      <c r="C7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.6832358674463938</v>
+      </c>
+      <c r="E7" t="n">
+        <v>132.2</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.2048192771084337</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.9156626506024096</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.2771084337349398</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.1927710843373494</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.8795180722891566</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.07228915662650602</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.07228915662650602</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.08433734939759036</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.07228915662650602</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.1204819277108434</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.1927710843373494</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.6867469879518072</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.03614457831325301</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.927710843373494</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.7108433734939759</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.1927710843373494</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0.02409638554216868</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.1807228915662651</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.541501976284585</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.5817174515235457</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0.2758620689655172</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0.09587020648967552</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0.5390070921985816</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0.1329113924050633</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0.1334569045412419</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0.2694444444444444</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0.004993757802746566</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0.1468531468531468</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>24</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>41</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>8</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="n">
+        <v>82</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.2812769048643995</v>
+      </c>
+      <c r="E8" t="n">
+        <v>74.16666666666666</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.1463414634146341</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.7195121951219512</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.1097560975609756</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.03658536585365853</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.1097560975609756</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.07317073170731707</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.03658536585365853</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.07317073170731707</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.1097560975609756</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.08536585365853659</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.03658536585365853</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.04878048780487805</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.04878048780487805</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.7804878048780488</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0.04878048780487805</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.1463414634146341</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0.5461525189786059</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0.5749698916097953</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0.2712609970674487</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0.0660927978856178</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0.5505555555555556</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0.1447908121410993</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0.1212560853725376</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0.2763429219507165</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0.03849052893753686</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0.1408043032786885</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>22</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>23</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>7</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>6</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="n">
+        <v>112</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.1052185163887292</v>
+      </c>
+      <c r="E9" t="n">
+        <v>28.025</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.08928571428571429</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.05357142857142857</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.2053571428571428</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.04464285714285714</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.9732142857142857</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.01785714285714286</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.03571428571428571</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.01785714285714286</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.07142857142857142</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.1071428571428571</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.1785714285714286</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.1339285714285714</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.08928571428571429</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.8660714285714286</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.08035714285714286</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.03571428571428571</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0.008928571428571428</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0.008928571428571428</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0.01785714285714286</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.1607142857142857</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0.5461355594869526</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0.5869666257379312</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0.2974358974358974</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0.1166980934422795</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0.5167906242956953</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0.1238776858971259</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0.1087885154061625</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0.01025641025641026</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0.1424668227946916</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>42</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>34</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="n">
+        <v>137</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.2352941176470588</v>
+      </c>
+      <c r="E10" t="n">
+        <v>49</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.3211678832116788</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.1167883211678832</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.1313868613138686</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.0583941605839416</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.0072992700729927</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.0145985401459854</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.0583941605839416</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.05109489051094891</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.072992700729927</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.1167883211678832</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.08759124087591241</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.9124087591240876</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.1021897810218978</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0.072992700729927</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0.0072992700729927</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0.0145985401459854</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.1824817518248175</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0.504424778761062</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0.6301075268817204</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0.3242009132420091</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0.1162790697674419</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0.4942528735632184</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0.1202185792349727</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0.105726872246696</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0.2312373225152129</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0.004566210045662105</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0.1333333333333333</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>51</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>31</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>17</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>8</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>7</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>11</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AU11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>cluster</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>size</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>median_n_lcr</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>median_coverage</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>median_mean_lcr_length</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>prop_domain_intrinsic</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>prop_domain_edge</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>prop_domain_adjacent</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>prop_interdomain_linker</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>prop_distal_terminal</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>prop_sig_rg_rgg_repeat_region</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>prop_sig_sr_rs_repeat_region</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>prop_sig_gs_rich_neutral_region</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>prop_sig_basic_enriched_region</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>prop_sig_arginine_rich_rna_contact_region</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>prop_sig_acidic_region</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>prop_sig_mixed_charge_polyampholyte</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>prop_sig_polar_linker</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>prop_sig_hydrophobic_region</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>prop_sig_aromatic_sticker_region</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>prop_sig_aromatic_aggregation_prone_region</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>prop_sig_cation_pi_rich_neighborhood</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>prop_sig_disorder_rich_spacer_region</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>prop_sig_serine_rich_region</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>prop_sig_glutamine_rich_region</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>prop_sig_glycine_rich_region</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>prop_sig_proline_rich_disordered_region</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>prop_sig_unmapped_physicochemical_properties</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>median_frac_polar</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>median_frac_hydrophobic</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>median_frac_strong_hydro</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>median_frac_aromatic</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>median_frac_disorder</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>median_frac_positive</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>median_frac_negative</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>median_fcr</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>median_ncpr</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>median_frac_GS</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>class_mRNA</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>class_unknown</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>class_tRNA</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>class_ribosomal protein</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>class_pre-rRNA</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>class_ncRNA</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>class_snRNA</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>class_snoRNA</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>class_diverse</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" t="n">
+        <v>144</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.2831315937261824</v>
+      </c>
+      <c r="E2" t="n">
+        <v>78.66666666666666</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.1180555555555556</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.09722222222222222</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.006944444444444444</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.03472222222222222</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.02777777777777778</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.04861111111111111</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.04861111111111111</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.06944444444444445</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.04166666666666666</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.7708333333333334</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.1388888888888889</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.04166666666666666</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.006944444444444444</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0.5208267716535433</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.6053392803822036</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0.2953799249530956</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0.109990926504688</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0.5158331625333059</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0.1309523809523809</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0.1058046125939363</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0.2469621470408253</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0.01675215540761759</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0.1357099959962632</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>59</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>39</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>13</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="n">
+        <v>128</v>
+      </c>
+      <c r="C3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.2825699276126221</v>
+      </c>
+      <c r="E3" t="n">
+        <v>56.875</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.046875</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.0859375</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.015625</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.0078125</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.015625</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.046875</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.0859375</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.078125</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.09375</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.0859375</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.1015625</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.890625</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.1875</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.1015625</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.03125</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.1796875</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.5226298080095005</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.6101963372380795</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.3100271002710027</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0.1106787750232003</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0.5149701359766172</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0.1178878568971448</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0.1143390744967836</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0.2363455809334657</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0.001190476190476191</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0.126832058339887</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>46</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>33</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>12</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>17</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>7</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="n">
+        <v>167</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.9812332439678284</v>
+      </c>
+      <c r="E4" t="n">
+        <v>229</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.005988023952095809</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.9281437125748503</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.08383233532934131</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.01197604790419162</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.1377245508982036</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.1377245508982036</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.1017964071856287</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.05988023952095808</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.01197604790419162</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.02395209580838323</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.01796407185628742</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.07784431137724551</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.005988023952095809</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.6706586826347305</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.2035928143712575</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.01197604790419162</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.03592814371257485</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.5186104218362283</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.6018957345971564</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.2938931297709923</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.0983606557377049</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.5327102803738317</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.1328125</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.116421568627451</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.2555970149253731</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0.01261829652996845</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.1433506044905009</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>65</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>41</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>9</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>16</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>11</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="n">
+        <v>59</v>
+      </c>
+      <c r="C5" t="n">
+        <v>7</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.2883895131086142</v>
+      </c>
+      <c r="E5" t="n">
+        <v>23.57142857142857</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.7627118644067796</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.9152542372881356</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.7966101694915254</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.3389830508474576</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.8305084745762712</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.01694915254237288</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.05084745762711865</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.06779661016949153</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.1694915254237288</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.2711864406779661</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.559322033898305</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.3389830508474576</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.5423728813559322</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.9491525423728814</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.288135593220339</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.7627118644067796</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0.1355932203389831</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.7288135593220338</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0.5183673469387755</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.5909090909090909</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0.2985074626865671</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0.5396825396825397</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0.1210526315789474</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0.1181818181818182</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0.2367601246105919</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>-0.004926108374384237</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0.1367924528301887</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>25</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>13</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>6</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>6</v>
+      </c>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="n">
+        <v>77</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.1186440677966102</v>
+      </c>
+      <c r="E6" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.09090909090909091</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.1428571428571428</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.5324675324675324</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.05194805194805195</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.1948051948051948</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.07792207792207792</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.05194805194805195</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.06493506493506493</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.02597402597402598</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.1428571428571428</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.2077922077922078</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.5844155844155844</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.01298701298701299</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.02597402597402598</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.07792207792207792</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.1168831168831169</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.09090909090909091</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.01298701298701299</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.01298701298701299</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.07792207792207792</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.6111111111111112</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.5245283018867924</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0.2425307557117751</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0.07207207207207207</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.5909090909090909</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0.169811320754717</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0.1710914454277286</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0.1370826010544816</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>37</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>17</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="n">
+        <v>87</v>
+      </c>
+      <c r="C7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.6592659719075669</v>
+      </c>
+      <c r="E7" t="n">
+        <v>132.2</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.1839080459770115</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.9195402298850575</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.264367816091954</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.1839080459770115</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.8850574712643678</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.06896551724137931</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.06896551724137931</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.09195402298850575</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.08045977011494253</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.103448275862069</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.2068965517241379</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.6551724137931034</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.04597701149425287</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.8735632183908046</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.7241379310344828</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.1839080459770115</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0.02298850574712644</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.1954022988505747</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.5405777166437414</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.5817174515235457</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0.2758620689655172</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0.09527220630372495</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0.5394736842105264</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0.1313725490196078</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0.1335260115606937</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0.2694444444444444</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0.003194888178913735</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0.1470588235294118</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>24</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>44</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>8</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="n">
+        <v>74</v>
+      </c>
+      <c r="C8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.2833341656187437</v>
+      </c>
+      <c r="E8" t="n">
+        <v>32.625</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.8513513513513513</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.1621621621621622</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.1621621621621622</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.08108108108108109</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.02702702702702703</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.04054054054054054</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.0945945945945946</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.1081081081081081</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.1351351351351351</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.2162162162162162</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.1621621621621622</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.9459459459459459</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.2297297297297297</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0.1216216216216216</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0.02702702702702703</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.2162162162162162</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0.5043863024240092</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0.6348076923076923</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0.3379488158899924</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0.1167197452229299</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0.4876470588235294</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0.1307911617961511</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0.1194059405940594</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0.006827700625340804</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0.1205381165919283</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>29</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>9</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>12</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>6</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>6</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="n">
+        <v>105</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.1040540540540541</v>
+      </c>
+      <c r="E9" t="n">
+        <v>28.25</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.06666666666666667</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.0380952380952381</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.1523809523809524</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.04761904761904762</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.9619047619047619</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.01904761904761905</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.02857142857142857</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.009523809523809525</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.08571428571428572</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.09523809523809523</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.1619047619047619</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.1047619047619048</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.1047619047619048</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.1142857142857143</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.0380952380952381</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0.009523809523809525</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0.009523809523809525</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0.01904761904761905</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.1238095238095238</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0.5305164319248825</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0.5929203539823009</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0.304093567251462</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0.1162790697674419</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0.5128205128205128</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0.1238615664845173</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0.1066666666666667</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0.247191011235955</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0.01025641025641026</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0.1428571428571428</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>41</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>29</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>8</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.04670227087366238</v>
+      </c>
+      <c r="E10" t="n">
+        <v>17.71428571428572</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.5517241379310345</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.293103448275862</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.05172413793103448</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.103448275862069</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.1724137931034483</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.01724137931034483</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.01724137931034483</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.103448275862069</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.08620689655172414</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.1206896551724138</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.08620689655172414</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.08620689655172414</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.1206896551724138</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0.08620689655172414</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.7931034482758621</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0.5164384795532337</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0.6159003831417624</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0.32612548741581</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0.05131578947368421</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0.5140168970814132</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0.1284340659340659</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0.2583333333333334</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0.1165158371040724</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>22</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>13</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>7</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>4</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AU10" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="n">
+        <v>69</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.06425702811244979</v>
+      </c>
+      <c r="E11" t="n">
+        <v>22.25</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.07246376811594203</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.1594202898550725</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.1739130434782609</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.01449275362318841</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.7536231884057971</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.02898550724637681</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.1449275362318841</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.05797101449275362</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.1014492753623188</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.07246376811594203</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.1739130434782609</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.02898550724637681</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.01449275362318841</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.02898550724637681</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0.1304347826086956</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0.1449275362318841</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0.6811594202898551</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0.01449275362318841</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0.04347826086956522</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.1014492753623188</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0.5555555555555556</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0.5060240963855421</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0.1866666666666667</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0.04587155963302753</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0.6774193548387096</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0.1573033707865168</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0.1224489795918367</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0.2709163346613546</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0.03370786516853932</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0.1971830985915493</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>29</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>16</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>5</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>6</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>